--- a/data/season_data.xlsx
+++ b/data/season_data.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Season Name</t>
   </si>
@@ -30,29 +25,41 @@
     <t>End Date</t>
   </si>
   <si>
+    <t>2020/21</t>
+  </si>
+  <si>
+    <t>2021/22</t>
+  </si>
+  <si>
+    <t>2022/23</t>
+  </si>
+  <si>
+    <t>2023/24</t>
+  </si>
+  <si>
     <t>2024/25</t>
   </si>
   <si>
-    <t>2023/24</t>
-  </si>
-  <si>
-    <t>2020/21</t>
-  </si>
-  <si>
-    <t>2021/22</t>
-  </si>
-  <si>
-    <t>2022/23</t>
-  </si>
-  <si>
     <t>2025/26</t>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2027-03-31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,7 +70,10 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,21 +116,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -408,15 +410,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -427,9 +425,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2">
         <v>43922</v>
@@ -438,9 +436,9 @@
         <v>44286</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
         <v>44287</v>
@@ -449,9 +447,9 @@
         <v>44651</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>44652</v>
@@ -460,9 +458,9 @@
         <v>45016</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
         <v>45017</v>
@@ -471,9 +469,9 @@
         <v>45382</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2">
         <v>45383</v>
@@ -482,7 +480,7 @@
         <v>45747</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -493,7 +491,18 @@
         <v>46112</v>
       </c>
     </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/season_data.xlsx
+++ b/data/season_data.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Season Name</t>
   </si>
@@ -44,22 +49,16 @@
   </si>
   <si>
     <t>2026/27</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2027-03-31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +122,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -169,7 +176,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -201,9 +208,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -235,6 +243,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -410,11 +419,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,7 +437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -436,7 +448,7 @@
         <v>44286</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -447,7 +459,7 @@
         <v>44651</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -458,7 +470,7 @@
         <v>45016</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -469,7 +481,7 @@
         <v>45382</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -480,7 +492,7 @@
         <v>45747</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -491,15 +503,15 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
+      <c r="B8" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C8" s="2">
+        <v>46477</v>
       </c>
     </row>
   </sheetData>
